--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0001T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.41501765494625</v>
+        <v>9.817440368928766</v>
       </c>
       <c r="D2" t="n">
-        <v>61.13599508954944</v>
+        <v>9.934599202051784</v>
       </c>
       <c r="E2" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F2" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.87987316249998</v>
+        <v>10.54297938890625</v>
       </c>
       <c r="D3" t="n">
-        <v>65.60105074621445</v>
+        <v>10.66017074625985</v>
       </c>
       <c r="E3" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F3" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.71948032002042</v>
+        <v>5.804415552003318</v>
       </c>
       <c r="D4" t="n">
-        <v>36.27913460674284</v>
+        <v>5.895359373595713</v>
       </c>
       <c r="E4" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F4" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.1531145413626</v>
+        <v>4.737381112971423</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82629133320224</v>
+        <v>4.846772341645364</v>
       </c>
       <c r="E5" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F5" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.56097306688559</v>
+        <v>6.591158123368908</v>
       </c>
       <c r="D6" t="n">
-        <v>41.58026808108393</v>
+        <v>6.756793563176139</v>
       </c>
       <c r="E6" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F6" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.72112931199659</v>
+        <v>6.292183513199446</v>
       </c>
       <c r="D7" t="n">
-        <v>38.34590152790363</v>
+        <v>6.23120899828434</v>
       </c>
       <c r="E7" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F7" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.51560137742012</v>
+        <v>6.58378522383077</v>
       </c>
       <c r="D8" t="n">
-        <v>40.6022373653542</v>
+        <v>6.597863571870057</v>
       </c>
       <c r="E8" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F8" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>64.90263331787541</v>
+        <v>10.54667791415475</v>
       </c>
       <c r="D9" t="n">
-        <v>64.38238614807453</v>
+        <v>10.46213774906211</v>
       </c>
       <c r="E9" t="n">
-        <v>13.312617382458</v>
+        <v>2.163300324649426</v>
       </c>
       <c r="F9" t="n">
-        <v>13.24131818083892</v>
+        <v>2.151714204386324</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
